--- a/mistral_translate_work/split_by_prompt/excel/ui/lang_text/lang_text__ui__part_0001.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/ui/lang_text/lang_text__ui__part_0001.xlsx
@@ -574,7 +574,7 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>Exit sau {0} giây</t>
+          <t>Thoát trong {0} giây</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Bạn cần xếp ít nhất một nhân vật vào đội</t>
+          <t>Bạn cần đặt ít nhất một Cộng Hưởng Giả vào đội hình.</t>
         </is>
       </c>
     </row>
@@ -769,7 +769,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Loại tinh nhuệ</t>
+          <t>Hạng Cao Cấp</t>
         </is>
       </c>
     </row>
@@ -899,7 +899,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Class Calamity</t>
+          <t>Hạng Thảm Họa</t>
         </is>
       </c>
     </row>
@@ -964,7 +964,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Resonance Terminal</t>
+          <t>Thiết Bị Đầu Cuối Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Vật liệu không đủ.</t>
+          <t>Vật liệu không đủ</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
     </row>
@@ -1289,7 +1289,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Di chuyển nhanh</t>
+          <t>D?ch chuy?n nhanh</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>Hạng Hợp Xướng</t>
+          <t>Hạng Hợp Ca</t>
         </is>
       </c>
     </row>
@@ -1549,7 +1549,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>Smelt</t>
+          <t>Cá Trích</t>
         </is>
       </c>
     </row>
@@ -1614,7 +1614,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>Conduction</t>
+          <t>Dẫn truyền</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>Aerodynamic</t>
+          <t>Khí Động Học</t>
         </is>
       </c>
     </row>
@@ -1744,7 +1744,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>Diffusion</t>
+          <t>Khuếch Tán</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>Dissociation</t>
+          <t>Phân Ly</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>Vật liệu không đủ.</t>
+          <t>Vật liệu không đủ</t>
         </is>
       </c>
     </row>
@@ -2004,7 +2004,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Được đảm bảo bởi uy tín của Sàn Giao Dịch, hai bên đồng ý giao dịch tài sản cơ sở hàng tháng theo giá cố định, và giá sẽ được điều chỉnh hàng ngày trước ngày đáo hạn dựa trên chênh lệch, với hình thức bồi thường là đặc quyền chấp nhận hoặc phiếu triều lưu, không bao gồm giao hàng vật lý.</t>
+          <t>Được đảm bảo bởi uy tín của Sàn Giao Dịch, các tài sản cơ sở sẽ được giao dịch hàng tháng với giá cố định, và giá sẽ được điều chỉnh hàng ngày trước ngày đáo hạn dựa trên chênh lệch, với khoản bồi thường dưới dạng đặc quyền chấp nhận hoặc phiếu ghi nợ cast tide, không có giao hàng vật lý.</t>
         </is>
       </c>
     </row>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Weapon</t>
+          <t>Vũ khí</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2199,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Cooking</t>
+          <t>Nấu ăn</t>
         </is>
       </c>
     </row>
@@ -2264,7 +2264,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Dish</t>
+          <t>Món ăn</t>
         </is>
       </c>
     </row>
@@ -2329,7 +2329,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Recipe</t>
+          <t>Công thức</t>
         </is>
       </c>
     </row>
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Cooking</t>
+          <t>Nấu ăn</t>
         </is>
       </c>
     </row>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Bond</t>
+          <t>Mối Liên Kết</t>
         </is>
       </c>
     </row>
@@ -2524,7 +2524,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách</t>
+          <t>Hoàn thành Thử thách</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2589,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách</t>
+          <t>Hoàn thành Thử thách</t>
         </is>
       </c>
     </row>
@@ -2654,7 +2654,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Vật liệu không đủ.</t>
+          <t>Vật liệu không đủ</t>
         </is>
       </c>
     </row>
@@ -2719,7 +2719,7 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>Material</t>
+          <t>Vật liệu</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>Dải sóng Cộng hưởng</t>
+          <t>Dải sóng Cộng Hưởng</t>
         </is>
       </c>
     </row>
@@ -2979,7 +2979,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Nhiệm Vụ General</t>
+          <t>Nhiệm vụ chung</t>
         </is>
       </c>
     </row>
@@ -3044,7 +3044,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Thư viện</t>
+          <t>Bộ Sưu Tập</t>
         </is>
       </c>
     </row>
